--- a/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、Atlatl；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、Atlatl；最直接一条：聚落可训长矛/掷矛</t>
+          <t>备选：原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 Atlatl、Hul'che Javelineers；最直接一条：步弓/掷矛生命+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -654,11 +654,11 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、Atlatl、Hul'che Javelineers；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -845,11 +845,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、Atlatl；最直接一条：聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
@@ -875,7 +875,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、Atlatl、Hul'che Javelineers；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、Hul'che Javelineers；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：长矛/掷矛移速+10%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 12/14。缺：帝王掷矛手、Atlatl</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>原生条目 1 条（强 1）；掷矛手科技树 12/14。缺：帝王掷矛手、掷矛器</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；掷矛手科技树 12/14。缺：Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 2 条（强 2）；掷矛手科技树 12/14。缺：掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3）；掷矛手科技树 8/14。缺：帝王掷矛手、扳指、弹道学、化学、Atlatl</t>
+          <t>原生条目 3 条（强 3）；掷矛手科技树 8/14。缺：帝王掷矛手、扳指、弹道学、化学、掷矛器</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 5）；掷矛手科技树 9/14。缺：帝王掷矛手、扳指、护腕、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 5 条（强 5）；掷矛手科技树 9/14。缺：帝王掷矛手、扳指、护腕、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、环甲、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、环甲、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、环甲、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 2 条（强 2）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、Atlatl、Hul'che Javelineers</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 8/14。缺：帝王掷矛手、弹道学、化学、环甲、Atlatl</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 8/14。缺：帝王掷矛手、弹道学、化学、环甲、掷矛器</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、Atlatl；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 Atlatl、Hul'che Javelineers；最直接一条：步弓/掷矛生命+20%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -3664,11 +3664,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、Atlatl；最直接一条：聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、Atlatl、Hul'che Javelineers；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、Atlatl、Hul'che Javelineers；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、Hul'che Javelineers；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：长矛/掷矛移速+10%</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、Atlatl、Hul'che Javelineers；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
     </row>

--- a/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·掷矛手本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与掷矛手流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·掷矛手本体强化'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·掷矛手本体强化'!$A$1:$E$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·掷矛手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与掷矛手流无关·可跳过'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与掷矛手流无关·可跳过'!$A$1:$D$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与掷矛手流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -584,7 +584,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
+          <t>备选：阶段1·本体强化；原生条目 10 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -654,11 +654,11 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、扳指、弹道学、化学；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、扳指、弹道学、化学；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -845,11 +845,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 10 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
@@ -875,7 +875,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -965,11 +965,11 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
@@ -995,11 +995,11 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -1055,11 +1055,11 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
@@ -1085,11 +1085,11 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>14</v>
       </c>
@@ -1115,11 +1115,11 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>15</v>
       </c>
@@ -1145,11 +1145,11 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>16</v>
       </c>
@@ -1175,12 +1175,42 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1192,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1777,22 +1807,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -1804,54 +1834,81 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>柏柏尔</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1962,12 +2019,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1994,7 +2051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2534,12 +2591,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2549,19 +2606,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2571,19 +2628,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2593,19 +2650,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2615,19 +2672,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2637,19 +2694,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2659,19 +2716,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2681,19 +2738,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2703,19 +2760,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2725,19 +2782,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2747,19 +2804,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2769,19 +2826,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2791,19 +2848,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2813,19 +2870,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2835,19 +2892,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2857,19 +2914,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2879,19 +2936,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2901,19 +2958,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2923,19 +2980,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2945,19 +3002,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2967,19 +3024,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2989,19 +3046,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3011,34 +3068,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采石村民缓慢获食」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强掷矛手</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D47"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3518,7 +3553,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -3544,7 +3579,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 12/14；缺 帝王掷矛手、掷矛器；最直接一条：胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3609,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 12/14；缺 掷矛器、胡尔切掷矛兵；最直接一条：步弓/掷矛生命+20%</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3634,12 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>精锐掷矛手升级免费；市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
+          <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、扳指、弹道学、化学；最直接一条：精锐掷矛手升级免费</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、扳指、弹道学、化学；最直接一条：精锐掷矛手升级免费</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3669,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）</t>
         </is>
       </c>
     </row>
@@ -3664,11 +3699,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 5 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 10 条（强 5 / 弱 0）；掷矛手科技树 9/14；缺 帝王掷矛手、扳指、护腕、掷矛器；最直接一条：聚落可训长矛/掷矛</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -3694,7 +3729,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3759,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、环甲、掷矛器、胡尔切掷矛兵；最直接一条：瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3789,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
       </c>
     </row>
@@ -3784,11 +3819,11 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -3814,11 +3849,11 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -3844,7 +3879,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、环甲、胡尔切掷矛兵；最直接一条：掷矛器（掷矛手攻+1，射程+1）</t>
         </is>
       </c>
     </row>
@@ -3874,11 +3909,11 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：长矛/掷矛移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -3904,11 +3939,11 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -3934,11 +3969,11 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -3964,11 +3999,11 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -3994,7 +4029,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
     </row>
@@ -4004,27 +4039,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强掷矛手</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4069,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4054,7 +4089,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4099,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4084,7 +4119,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4129,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4114,7 +4149,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4159,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -4144,7 +4179,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4189,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -4174,7 +4209,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4219,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4204,7 +4239,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4249,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4234,7 +4269,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4279,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4264,7 +4299,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4309,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4294,7 +4329,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4339,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -4324,7 +4359,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4369,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -4354,7 +4389,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4399,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -4384,7 +4419,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4429,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -4414,7 +4449,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4459,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -4444,7 +4479,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4489,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -4474,7 +4509,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4519,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -4504,7 +4539,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4549,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -4534,7 +4569,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4579,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -4564,7 +4599,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4609,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -4594,7 +4629,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4639,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -4624,7 +4659,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4669,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -4654,7 +4689,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4699,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -4684,7 +4719,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4729,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -4714,7 +4749,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5510,101 +5545,141 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>① 只看直接作用于掷矛手本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr"/>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与掷矛手流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
+          <t>直接加强掷矛手本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（靶场远程系（掷矛手/投石手等））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="11" t="inlineStr"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与掷矛手流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A21" s="11" t="inlineStr"/>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 掷矛手流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·掷矛手本体强化'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·掷矛手本体强化'!$A$1:$E$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·掷矛手本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与掷矛手流无关·可跳过'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与掷矛手流无关·可跳过'!$A$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与掷矛手流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -73,7 +73,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +93,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,10 +160,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -654,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -746,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -875,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1073,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1075,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1085,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1105,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1115,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1135,27 +1143,27 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1165,17 +1173,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -1209,8 +1217,68 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 10/14；缺 帝王掷矛手、护腕、掷矛器、胡尔切掷矛兵</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1222,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1260,7 +1328,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1287,7 +1355,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1314,7 +1382,7 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1341,7 +1409,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1368,7 +1436,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1807,22 +1875,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1834,81 +1902,54 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
           <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1920,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1958,7 +1999,7 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2012,34 +2053,142 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>靶场/兵营升级食物-50%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2051,7 +2200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2393,12 +2542,12 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2408,19 +2557,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>海军文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2430,19 +2579,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2452,19 +2601,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2474,19 +2623,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2496,19 +2645,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>象兵和海军文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2518,19 +2667,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>象兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2540,19 +2689,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2562,19 +2711,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>骑兵和骆驼文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2584,19 +2733,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2606,19 +2755,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2628,19 +2777,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2650,19 +2799,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2672,19 +2821,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2694,19 +2843,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2716,19 +2865,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2738,19 +2887,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2760,14 +2909,14 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2782,19 +2931,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2804,19 +2953,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2826,19 +2975,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2848,19 +2997,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2870,19 +3019,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始石料+100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2892,19 +3041,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2914,19 +3063,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2936,19 +3085,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2958,19 +3107,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2980,19 +3129,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3002,19 +3151,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3024,56 +3173,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「高地受伤-10%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强掷矛手</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采石村民缓慢获食」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强掷矛手</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3268,7 +3373,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵</t>
+          <t>原生条目 2 条（强 1）；掷矛手科技树 10/14。缺：帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3533,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3438,7 +3543,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3453,22 +3558,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 8/14。缺：帝王掷矛手、弹道学、化学、环甲、掷矛器</t>
         </is>
       </c>
     </row>
@@ -3478,22 +3583,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；掷矛手科技树 8/14。缺：帝王掷矛手、弹道学、化学、环甲、掷矛器</t>
+          <t>原生条目 1 条（强 1）；掷矛手科技树 11/14。缺：帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3667,7 @@
           <t>玛雅</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3572,7 +3677,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>胡尔切掷矛兵（掷矛手额外投掷一支长矛）</t>
         </is>
@@ -3592,7 +3697,7 @@
           <t>越南</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3602,7 +3707,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>步弓/掷矛生命+20%；在帝王时代可升级为帝王掷矛手</t>
         </is>
@@ -3622,7 +3727,7 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3632,7 +3737,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>市政/古典掷矛手每分钟回5/10生命；轻装盾兵（掷矛手造成穿透伤害）</t>
         </is>
@@ -3662,7 +3767,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>安第斯弹弓（掷矛手/投石手无最小射程；投石手攻+1）；织物盾（印加枪兵长/投石手/蔷琵战士近战护甲+1/远程护甲+1）</t>
         </is>
@@ -3692,7 +3797,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>聚落可训长矛/掷矛；步兵/投石手/掷矛封建/城堡/帝王生命+5/10/15；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
@@ -3722,14 +3827,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；掷矛手科技树 10/14；缺 帝王掷矛手、扳指、掷矛器、胡尔切掷矛兵；最直接一条：卡西克（蔷琵战士/投石手攻速+25%）</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3857,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>瓦拉卡斯（投石手射程+1；训练+50%）</t>
         </is>
@@ -3782,7 +3887,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>英皇侍卫（步弓手/掷矛手系射程+1；瞭望箭塔系攻+2）</t>
         </is>
@@ -3812,7 +3917,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
@@ -3842,7 +3947,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>掷矛/长矛/斥候骑兵系训练升级+15%；札甲（步兵/掷矛手反弹25%近战伤害）</t>
         </is>
@@ -3919,7 +4024,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3934,12 +4039,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
         </is>
       </c>
     </row>
@@ -3949,7 +4054,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3964,12 +4069,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：步弓手和掷矛手对建筑的攻击力 +2</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4084,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3994,22 +4099,22 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>希洛人征兵（长矛/掷矛/村民训练+50%）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 8/14；缺 帝王掷矛手、弹道学、化学、环甲；最直接一条：希洛人征兵（长矛/掷矛/村民训练+50%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4024,12 +4129,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -4069,27 +4174,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强掷矛手</t>
+          <t>弓兵靶场/铁匠铺科技-25%</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 11/14；缺 帝王掷矛手、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -4099,27 +4204,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强掷矛手</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；掷矛手科技树 10/14；缺 帝王掷矛手、护腕、掷矛器、胡尔切掷矛兵</t>
         </is>
       </c>
     </row>
@@ -4129,10 +4234,10 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4149,7 +4254,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4264,10 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4179,7 +4284,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -4189,10 +4294,10 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4209,7 +4314,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4219,10 +4324,10 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4239,7 +4344,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4354,10 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4269,7 +4374,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4279,10 +4384,10 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4299,7 +4404,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4309,10 +4414,10 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4329,7 +4434,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4339,10 +4444,10 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4359,7 +4464,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -4369,10 +4474,10 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4389,7 +4494,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4399,10 +4504,10 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4419,7 +4524,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4429,10 +4534,10 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4449,7 +4554,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局有骡车」）</t>
+          <t>攻城武器和大象文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「无需建筑即可升时代/解锁建筑」）</t>
         </is>
       </c>
     </row>
@@ -4459,10 +4564,10 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4479,7 +4584,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4489,10 +4594,10 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4509,7 +4614,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -4519,10 +4624,10 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4539,7 +4644,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4549,10 +4654,10 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4569,7 +4674,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -4579,10 +4684,10 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4599,7 +4704,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代速度+66%」）</t>
         </is>
       </c>
     </row>
@@ -4609,10 +4714,10 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4629,7 +4734,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -4639,10 +4744,10 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4659,7 +4764,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -4669,10 +4774,10 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4689,7 +4794,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -4699,10 +4804,10 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4719,7 +4824,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
+          <t>象兵和海军文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「升时代TC产生2村民」）</t>
         </is>
       </c>
     </row>
@@ -4729,10 +4834,10 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4749,7 +4854,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4759,10 +4864,10 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4779,7 +4884,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4789,10 +4894,10 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4809,7 +4914,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骑兵和骆驼文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「开局2果树丛」）</t>
         </is>
       </c>
     </row>
@@ -4819,10 +4924,10 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4839,7 +4944,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
@@ -4849,10 +4954,10 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4869,7 +4974,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于掷矛手。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4987,7 @@
           <t>斯拉夫</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4912,7 +5017,7 @@
           <t>条顿</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4942,7 +5047,7 @@
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4972,7 +5077,7 @@
           <t>瓦兰吉人</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5002,7 +5107,7 @@
           <t>维京</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5032,7 +5137,7 @@
           <t>魏</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5062,7 +5167,7 @@
           <t>吴</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5092,7 +5197,7 @@
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5122,7 +5227,7 @@
           <t>西西里</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5152,7 +5257,7 @@
           <t>匈奴</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5182,7 +5287,7 @@
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5212,7 +5317,7 @@
           <t>意大利</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5242,7 +5347,7 @@
           <t>印度斯坦</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5272,7 +5377,7 @@
           <t>中国</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5302,7 +5407,7 @@
           <t>阿契美尼德</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5332,7 +5437,7 @@
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5362,7 +5467,7 @@
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5392,7 +5497,7 @@
           <t>雅典</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5434,252 +5539,252 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>《帝国时代2 决定版》掷矛手流最优研究顺序</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>By RemonBo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="12" t="inlineStr"/>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr"/>
     </row>
     <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>口径</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>62 个按钮 = 各文明的全部特性（主要功能 + 独特科技 + 团队加成），不含独特单位。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>团队加成按「对自己生效」计算，不因原本是全队加成而降权。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="11" t="inlineStr"/>
-      <c r="B5" s="11" t="inlineStr"/>
+      <c r="A5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>决定性前提 1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>掷矛手出自靶场，封建时代即有，造价低（食物 + 木材），是标准的反弓兵兵种与消耗品。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>决定性前提 2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>掷矛手怕骑兵与攻城武器；射速（扳指）与射程是最核心的两项。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>决定性前提 3</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>掷矛手基础伤害很低，「额外投一支矛」或「穿透伤害」类效果等于成倍提升输出。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="11" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>模组专属：按钮机制</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>模组专属：无专属机制</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>已确认模组文本（v21）中没有任何针对掷矛手的独立按钮或 SSR 互斥项。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>① 阶段 1 · 本体强化</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>直接加强掷矛手本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>② 阶段 2 · 减费用</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>降低该兵种及同系兵种（靶场远程系（掷矛手/投石手等））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>③ 阶段 3 · 资源效率</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr"/>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与掷矛手流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr"/>
+      <c r="B18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr"/>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr"/>
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>数据来源</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>
